--- a/Stats Sheet/Round Gaps/Reps Rumble.xlsx
+++ b/Stats Sheet/Round Gaps/Reps Rumble.xlsx
@@ -418,13 +418,13 @@
     <x:t>kirbey</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
-  </x:si>
-  <x:si>
     <x:t>MaxEvasion</x:t>
   </x:si>
   <x:si>
     <x:t>MeadowMoos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>OddishThoughts</x:t>
@@ -3379,10 +3379,10 @@
       <x:c r="H109" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K109" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
       <x:c r="L109" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="M109" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -3397,15 +3397,9 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H110" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L110" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="M110" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -3420,9 +3414,15 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D111" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H111" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K111" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="L111" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
